--- a/projetos/gestao-ia-planilhas/produto/kit-completo/07-orcamento-previsto-x-realizado.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/07-orcamento-previsto-x-realizado.xlsx
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -963,34 +963,58 @@
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/07-orcamento-previsto-x-realizado.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/07-orcamento-previsto-x-realizado.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>95559.34</v>
+        <v>131200</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15">
@@ -1109,12 +1109,12 @@
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="17">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>81387.49</v>
+        <v>89800</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="18">
         <f>C5-G5</f>
-        <v>14171.85</v>
+        <v>41400</v>
       </c>
       <c r="J5" s="14" t="n"/>
     </row>
@@ -1187,19 +1187,19 @@
       </c>
       <c r="D9" s="23">
         <f>IF(Config!$A$12="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$12,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>65593.42</v>
+        <v>90057.73</v>
       </c>
       <c r="E9" s="23">
         <f>IF(Config!$A$12="","",D9-C9)</f>
-        <v>-406.580000000002</v>
+        <v>24057.73</v>
       </c>
       <c r="F9" s="24">
         <f>IF(OR(Config!$A$12="",C9=0),"",E9/C9)</f>
-        <v>-0.00616030303030306</v>
+        <v>0.364511060606061</v>
       </c>
       <c r="G9" s="22" t="str">
         <f>IF(Config!$A$12="","",IF(B9="Despesa",IF(AND(C9&gt;0,F9&gt;Config!$B$8),"Estourou",IF(D9&gt;C9,"Acima","Dentro")),IF(AND(C9&gt;0,F9&lt;-Config!$B$8),"Abaixo da meta",IF(D9&gt;=C9,"Meta batida","Perto da meta"))))</f>
-        <v>Perto da meta</v>
+        <v>Meta batida</v>
       </c>
       <c r="H9" s="23">
         <f>IF(Config!$A$12="","",SUM(INDEX(Previsto!$B$5:$M$5,1,1):INDEX(Previsto!$B$5:$M$5,1,Config!$B$7)))</f>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I9" s="23">
         <f>IF(Config!$A$12="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$12,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>519718.65</v>
+        <v>727249.28</v>
       </c>
     </row>
     <row r="10">
@@ -1225,15 +1225,15 @@
       </c>
       <c r="D10" s="23">
         <f>IF(Config!$A$13="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$13,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>26534.91</v>
+        <v>36431.6</v>
       </c>
       <c r="E10" s="23">
         <f>IF(Config!$A$13="","",D10-C10)</f>
-        <v>534.91</v>
+        <v>10431.6</v>
       </c>
       <c r="F10" s="24">
         <f>IF(OR(Config!$A$13="",C10=0),"",E10/C10)</f>
-        <v>0.0205734615384615</v>
+        <v>0.401215384615385</v>
       </c>
       <c r="G10" s="22" t="str">
         <f>IF(Config!$A$13="","",IF(B10="Despesa",IF(AND(C10&gt;0,F10&gt;Config!$B$8),"Estourou",IF(D10&gt;C10,"Acima","Dentro")),IF(AND(C10&gt;0,F10&lt;-Config!$B$8),"Abaixo da meta",IF(D10&gt;=C10,"Meta batida","Perto da meta"))))</f>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I10" s="23">
         <f>IF(Config!$A$13="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$13,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>199168.99</v>
+        <v>278713.88</v>
       </c>
     </row>
     <row r="11">
@@ -1263,15 +1263,15 @@
       </c>
       <c r="D11" s="23">
         <f>IF(Config!$A$14="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$14,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>3431.01</v>
+        <v>4710.67</v>
       </c>
       <c r="E11" s="23">
         <f>IF(Config!$A$14="","",D11-C11)</f>
-        <v>431.01</v>
+        <v>1710.67</v>
       </c>
       <c r="F11" s="24">
         <f>IF(OR(Config!$A$14="",C11=0),"",E11/C11)</f>
-        <v>0.14367</v>
+        <v>0.570223333333333</v>
       </c>
       <c r="G11" s="22" t="str">
         <f>IF(Config!$A$14="","",IF(B11="Despesa",IF(AND(C11&gt;0,F11&gt;Config!$B$8),"Estourou",IF(D11&gt;C11,"Acima","Dentro")),IF(AND(C11&gt;0,F11&lt;-Config!$B$8),"Abaixo da meta",IF(D11&gt;=C11,"Meta batida","Perto da meta"))))</f>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="I11" s="23">
         <f>IF(Config!$A$14="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$14,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>19802.13</v>
+        <v>27636.84</v>
       </c>
     </row>
     <row r="12">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="D12" s="23">
         <f>IF(Config!$A$15="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$15,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>41722.62</v>
+        <v>46035.22</v>
       </c>
       <c r="E12" s="23">
         <f>IF(Config!$A$15="","",D12-C12)</f>
-        <v>722.620000000003</v>
+        <v>5035.22</v>
       </c>
       <c r="F12" s="24">
         <f>IF(OR(Config!$A$15="",C12=0),"",E12/C12)</f>
-        <v>0.0176248780487806</v>
+        <v>0.122810243902439</v>
       </c>
       <c r="G12" s="22" t="str">
         <f>IF(Config!$A$15="","",IF(B12="Despesa",IF(AND(C12&gt;0,F12&gt;Config!$B$8),"Estourou",IF(D12&gt;C12,"Acima","Dentro")),IF(AND(C12&gt;0,F12&lt;-Config!$B$8),"Abaixo da meta",IF(D12&gt;=C12,"Meta batida","Perto da meta"))))</f>
-        <v>Acima</v>
+        <v>Estourou</v>
       </c>
       <c r="H12" s="23">
         <f>IF(Config!$A$15="","",SUM(INDEX(Previsto!$B$8:$M$8,1,1):INDEX(Previsto!$B$8:$M$8,1,Config!$B$7)))</f>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I12" s="23">
         <f>IF(Config!$A$15="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$15,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>352675.89</v>
+        <v>403904.76</v>
       </c>
     </row>
     <row r="13">
@@ -1339,15 +1339,15 @@
       </c>
       <c r="D13" s="23">
         <f>IF(Config!$A$16="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$16,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>10749.54</v>
+        <v>11860.65</v>
       </c>
       <c r="E13" s="23">
         <f>IF(Config!$A$16="","",D13-C13)</f>
-        <v>1749.54</v>
+        <v>2860.65</v>
       </c>
       <c r="F13" s="24">
         <f>IF(OR(Config!$A$16="",C13=0),"",E13/C13)</f>
-        <v>0.194393333333333</v>
+        <v>0.31785</v>
       </c>
       <c r="G13" s="22" t="str">
         <f>IF(Config!$A$16="","",IF(B13="Despesa",IF(AND(C13&gt;0,F13&gt;Config!$B$8),"Estourou",IF(D13&gt;C13,"Acima","Dentro")),IF(AND(C13&gt;0,F13&lt;-Config!$B$8),"Abaixo da meta",IF(D13&gt;=C13,"Meta batida","Perto da meta"))))</f>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="I13" s="23">
         <f>IF(Config!$A$16="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$16,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>83952.45</v>
+        <v>96081.15</v>
       </c>
     </row>
     <row r="14">
@@ -1377,19 +1377,19 @@
       </c>
       <c r="D14" s="23">
         <f>IF(Config!$A$17="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$17,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>4257.16</v>
+        <v>4697.2</v>
       </c>
       <c r="E14" s="23">
         <f>IF(Config!$A$17="","",D14-C14)</f>
-        <v>57.1599999999999</v>
+        <v>497.2</v>
       </c>
       <c r="F14" s="24">
         <f>IF(OR(Config!$A$17="",C14=0),"",E14/C14)</f>
-        <v>0.0136095238095238</v>
+        <v>0.118380952380952</v>
       </c>
       <c r="G14" s="22" t="str">
         <f>IF(Config!$A$17="","",IF(B14="Despesa",IF(AND(C14&gt;0,F14&gt;Config!$B$8),"Estourou",IF(D14&gt;C14,"Acima","Dentro")),IF(AND(C14&gt;0,F14&lt;-Config!$B$8),"Abaixo da meta",IF(D14&gt;=C14,"Meta batida","Perto da meta"))))</f>
-        <v>Acima</v>
+        <v>Estourou</v>
       </c>
       <c r="H14" s="23">
         <f>IF(Config!$A$17="","",SUM(INDEX(Previsto!$B$10:$M$10,1,1):INDEX(Previsto!$B$10:$M$10,1,Config!$B$7)))</f>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="I14" s="23">
         <f>IF(Config!$A$17="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$17,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>39310.67</v>
+        <v>45082.77</v>
       </c>
     </row>
     <row r="15">
@@ -1415,15 +1415,15 @@
       </c>
       <c r="D15" s="23">
         <f>IF(Config!$A$18="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$18,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>2209.34</v>
+        <v>2437.71</v>
       </c>
       <c r="E15" s="23">
         <f>IF(Config!$A$18="","",D15-C15)</f>
-        <v>309.34</v>
+        <v>537.71</v>
       </c>
       <c r="F15" s="24">
         <f>IF(OR(Config!$A$18="",C15=0),"",E15/C15)</f>
-        <v>0.16281052631579</v>
+        <v>0.283005263157895</v>
       </c>
       <c r="G15" s="22" t="str">
         <f>IF(Config!$A$18="","",IF(B15="Despesa",IF(AND(C15&gt;0,F15&gt;Config!$B$8),"Estourou",IF(D15&gt;C15,"Acima","Dentro")),IF(AND(C15&gt;0,F15&lt;-Config!$B$8),"Abaixo da meta",IF(D15&gt;=C15,"Meta batida","Perto da meta"))))</f>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I15" s="23">
         <f>IF(Config!$A$18="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$18,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>19110.46</v>
+        <v>21926.17</v>
       </c>
     </row>
     <row r="16">
@@ -1453,15 +1453,15 @@
       </c>
       <c r="D16" s="23">
         <f>IF(Config!$A$19="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$19,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>6510.99</v>
+        <v>7183.98</v>
       </c>
       <c r="E16" s="23">
         <f>IF(Config!$A$19="","",D16-C16)</f>
-        <v>1510.99</v>
+        <v>2183.98</v>
       </c>
       <c r="F16" s="24">
         <f>IF(OR(Config!$A$19="",C16=0),"",E16/C16)</f>
-        <v>0.302198</v>
+        <v>0.436796</v>
       </c>
       <c r="G16" s="22" t="str">
         <f>IF(Config!$A$19="","",IF(B16="Despesa",IF(AND(C16&gt;0,F16&gt;Config!$B$8),"Estourou",IF(D16&gt;C16,"Acima","Dentro")),IF(AND(C16&gt;0,F16&lt;-Config!$B$8),"Abaixo da meta",IF(D16&gt;=C16,"Meta batida","Perto da meta"))))</f>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="I16" s="23">
         <f>IF(Config!$A$19="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$19,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>45451.52</v>
+        <v>51925.54</v>
       </c>
     </row>
     <row r="17">
@@ -1491,19 +1491,19 @@
       </c>
       <c r="D17" s="23">
         <f>IF(Config!$A$20="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$20,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>10137.12</v>
+        <v>11184.93</v>
       </c>
       <c r="E17" s="23">
         <f>IF(Config!$A$20="","",D17-C17)</f>
-        <v>-62.8799999999992</v>
+        <v>984.93</v>
       </c>
       <c r="F17" s="24">
         <f>IF(OR(Config!$A$20="",C17=0),"",E17/C17)</f>
-        <v>-0.00616470588235286</v>
+        <v>0.0965617647058824</v>
       </c>
       <c r="G17" s="22" t="str">
         <f>IF(Config!$A$20="","",IF(B17="Despesa",IF(AND(C17&gt;0,F17&gt;Config!$B$8),"Estourou",IF(D17&gt;C17,"Acima","Dentro")),IF(AND(C17&gt;0,F17&lt;-Config!$B$8),"Abaixo da meta",IF(D17&gt;=C17,"Meta batida","Perto da meta"))))</f>
-        <v>Dentro</v>
+        <v>Acima</v>
       </c>
       <c r="H17" s="23">
         <f>IF(Config!$A$20="","",SUM(INDEX(Previsto!$B$13:$M$13,1,1):INDEX(Previsto!$B$13:$M$13,1,Config!$B$7)))</f>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="I17" s="23">
         <f>IF(Config!$A$20="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$20,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>83612.75</v>
+        <v>95809.56</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I18" s="23">
         <f>IF(Config!$A$21="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$21,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>7026.92</v>
+        <v>7602.07</v>
       </c>
     </row>
     <row r="19">
@@ -1567,15 +1567,15 @@
       </c>
       <c r="D19" s="23">
         <f>IF(Config!$A$22="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$22,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>198.64</v>
+        <v>219.18</v>
       </c>
       <c r="E19" s="23">
         <f>IF(Config!$A$22="","",D19-C19)</f>
-        <v>-301.36</v>
+        <v>-280.82</v>
       </c>
       <c r="F19" s="24">
         <f>IF(OR(Config!$A$22="",C19=0),"",E19/C19)</f>
-        <v>-0.60272</v>
+        <v>-0.56164</v>
       </c>
       <c r="G19" s="22" t="str">
         <f>IF(Config!$A$22="","",IF(B19="Despesa",IF(AND(C19&gt;0,F19&gt;Config!$B$8),"Estourou",IF(D19&gt;C19,"Acima","Dentro")),IF(AND(C19&gt;0,F19&lt;-Config!$B$8),"Abaixo da meta",IF(D19&gt;=C19,"Meta batida","Perto da meta"))))</f>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="I19" s="23">
         <f>IF(Config!$A$22="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$22,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>1815.27</v>
+        <v>2083.46</v>
       </c>
     </row>
     <row r="20">
@@ -1605,15 +1605,15 @@
       </c>
       <c r="D20" s="23">
         <f>IF(Config!$A$23="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$23,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>2717.27</v>
+        <v>2998.14</v>
       </c>
       <c r="E20" s="23">
         <f>IF(Config!$A$23="","",D20-C20)</f>
-        <v>-282.73</v>
+        <v>-1.86000000000013</v>
       </c>
       <c r="F20" s="24">
         <f>IF(OR(Config!$A$23="",C20=0),"",E20/C20)</f>
-        <v>-0.0942433333333334</v>
+        <v>-0.000620000000000042</v>
       </c>
       <c r="G20" s="22" t="str">
         <f>IF(Config!$A$23="","",IF(B20="Despesa",IF(AND(C20&gt;0,F20&gt;Config!$B$8),"Estourou",IF(D20&gt;C20,"Acima","Dentro")),IF(AND(C20&gt;0,F20&lt;-Config!$B$8),"Abaixo da meta",IF(D20&gt;=C20,"Meta batida","Perto da meta"))))</f>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I20" s="23">
         <f>IF(Config!$A$23="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$23,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>10012.63</v>
+        <v>11474.82</v>
       </c>
     </row>
     <row r="21">
@@ -1643,19 +1643,19 @@
       </c>
       <c r="D21" s="23">
         <f>IF(Config!$A$24="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$24,Realizado!$F$5:$F$604,Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>2884.81</v>
+        <v>3182.99</v>
       </c>
       <c r="E21" s="23">
         <f>IF(Config!$A$24="","",D21-C21)</f>
-        <v>-115.19</v>
+        <v>182.99</v>
       </c>
       <c r="F21" s="24">
         <f>IF(OR(Config!$A$24="",C21=0),"",E21/C21)</f>
-        <v>-0.0383966666666667</v>
+        <v>0.0609966666666666</v>
       </c>
       <c r="G21" s="22" t="str">
         <f>IF(Config!$A$24="","",IF(B21="Despesa",IF(AND(C21&gt;0,F21&gt;Config!$B$8),"Estourou",IF(D21&gt;C21,"Acima","Dentro")),IF(AND(C21&gt;0,F21&lt;-Config!$B$8),"Abaixo da meta",IF(D21&gt;=C21,"Meta batida","Perto da meta"))))</f>
-        <v>Dentro</v>
+        <v>Acima</v>
       </c>
       <c r="H21" s="23">
         <f>IF(Config!$A$24="","",SUM(INDEX(Previsto!$B$17:$M$17,1,1):INDEX(Previsto!$B$17:$M$17,1,Config!$B$7)))</f>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="I21" s="23">
         <f>IF(Config!$A$24="","",SUMIFS(Realizado!$D$5:$D$604,Realizado!$B$5:$B$604,Config!$A$24,Realizado!$F$5:$F$604,"&lt;="&amp;Config!$B$7,Realizado!$G$5:$G$604,Config!$B$5))</f>
-        <v>26763.1</v>
+        <v>30709.7</v>
       </c>
     </row>
     <row r="22">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C32" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,1,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>68436.54</v>
+        <v>98500</v>
       </c>
       <c r="D32" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,1),Config!$B$12:$B$31,"Despesa")</f>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E32" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,1,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>68195.56</v>
+        <v>80200</v>
       </c>
       <c r="F32" s="23">
         <f>B32-D32</f>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="G32" s="23">
         <f>C32-E32</f>
-        <v>240.979999999996</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="33">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="C33" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,2,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>72382.24</v>
+        <v>101200</v>
       </c>
       <c r="D33" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,2),Config!$B$12:$B$31,"Despesa")</f>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E33" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,2,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>68512.13</v>
+        <v>81900</v>
       </c>
       <c r="F33" s="23">
         <f>B33-D33</f>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="G33" s="23">
         <f>C33-E33</f>
-        <v>3870.11</v>
+        <v>19300</v>
       </c>
     </row>
     <row r="34">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C34" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,3,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>79418.93</v>
+        <v>112400</v>
       </c>
       <c r="D34" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,3),Config!$B$12:$B$31,"Despesa")</f>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E34" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,3,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>75904.68</v>
+        <v>84100</v>
       </c>
       <c r="F34" s="23">
         <f>B34-D34</f>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G34" s="23">
         <f>C34-E34</f>
-        <v>3514.25</v>
+        <v>28300</v>
       </c>
     </row>
     <row r="35">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C35" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,4,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>79171.73</v>
+        <v>109800</v>
       </c>
       <c r="D35" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,4),Config!$B$12:$B$31,"Despesa")</f>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E35" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,4,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>72484.05</v>
+        <v>86500</v>
       </c>
       <c r="F35" s="23">
         <f>B35-D35</f>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G35" s="23">
         <f>C35-E35</f>
-        <v>6687.67999999999</v>
+        <v>23300</v>
       </c>
     </row>
     <row r="36">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C36" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,5,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>84895.22</v>
+        <v>118300</v>
       </c>
       <c r="D36" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,5),Config!$B$12:$B$31,"Despesa")</f>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="E36" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,5,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>72272.98</v>
+        <v>83700</v>
       </c>
       <c r="F36" s="23">
         <f>B36-D36</f>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="G36" s="23">
         <f>C36-E36</f>
-        <v>12622.24</v>
+        <v>34600</v>
       </c>
     </row>
     <row r="37">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C37" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,6,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>82906.89</v>
+        <v>121900</v>
       </c>
       <c r="D37" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,6),Config!$B$12:$B$31,"Despesa")</f>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E37" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,6,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>71740.09</v>
+        <v>88200</v>
       </c>
       <c r="F37" s="23">
         <f>B37-D37</f>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="G37" s="23">
         <f>C37-E37</f>
-        <v>11166.8</v>
+        <v>33700</v>
       </c>
     </row>
     <row r="38">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C38" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,7,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>89625.23</v>
+        <v>115700</v>
       </c>
       <c r="D38" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,7),Config!$B$12:$B$31,"Despesa")</f>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E38" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,7,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>81289.98</v>
+        <v>84900</v>
       </c>
       <c r="F38" s="23">
         <f>B38-D38</f>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G38" s="23">
         <f>C38-E38</f>
-        <v>8335.25</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="39">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C39" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,8,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>86293.65</v>
+        <v>124600</v>
       </c>
       <c r="D39" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,8),Config!$B$12:$B$31,"Despesa")</f>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="E39" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,8,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>77944.7</v>
+        <v>87300</v>
       </c>
       <c r="F39" s="23">
         <f>B39-D39</f>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="G39" s="23">
         <f>C39-E39</f>
-        <v>8348.95</v>
+        <v>37300</v>
       </c>
     </row>
     <row r="40">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C40" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Receita",Realizado!$F$5:$F$604,9,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>95559.34</v>
+        <v>131200</v>
       </c>
       <c r="D40" s="23">
         <f>SUMIFS(INDEX(Previsto!$B$5:$M$24,0,9),Config!$B$12:$B$31,"Despesa")</f>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E40" s="23">
         <f>SUMIFS(Realizado!$D$5:$D$604,Realizado!$H$5:$H$604,"Despesa",Realizado!$F$5:$F$604,9,Realizado!$G$5:$G$604,Config!$B$5)</f>
-        <v>81387.49</v>
+        <v>89800</v>
       </c>
       <c r="F40" s="23">
         <f>B40-D40</f>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G40" s="23">
         <f>C40-E40</f>
-        <v>14171.85</v>
+        <v>41400</v>
       </c>
     </row>
     <row r="41">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>48873.54</v>
+        <v>70343.17999999999</v>
       </c>
       <c r="E5" s="27" t="n"/>
       <c r="F5" s="22">
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="D6" s="35" t="n">
-        <v>18424.96</v>
+        <v>26518.86</v>
       </c>
       <c r="E6" s="27" t="n"/>
       <c r="F6" s="22">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>1138.04</v>
+        <v>1637.96</v>
       </c>
       <c r="E7" s="27" t="n"/>
       <c r="F7" s="22">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="D8" s="35" t="n">
-        <v>38315.92</v>
+        <v>45060.66</v>
       </c>
       <c r="E8" s="27" t="n"/>
       <c r="F8" s="22">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>7393.62</v>
+        <v>8695.120000000001</v>
       </c>
       <c r="E9" s="27" t="n"/>
       <c r="F9" s="22">
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="D10" s="35" t="n">
-        <v>4175.64</v>
+        <v>4910.67</v>
       </c>
       <c r="E10" s="27" t="n"/>
       <c r="F10" s="22">
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>2045.12</v>
+        <v>2405.12</v>
       </c>
       <c r="E11" s="27" t="n"/>
       <c r="F11" s="22">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D12" s="35" t="n">
-        <v>4005.29</v>
+        <v>4710.34</v>
       </c>
       <c r="E12" s="27" t="n"/>
       <c r="F12" s="22">
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="D13" s="35" t="n">
-        <v>8253</v>
+        <v>9705.77</v>
       </c>
       <c r="E13" s="27" t="n"/>
       <c r="F13" s="22">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="D14" s="35" t="n">
-        <v>207.93</v>
+        <v>244.53</v>
       </c>
       <c r="E14" s="27" t="n"/>
       <c r="F14" s="22">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="D15" s="35" t="n">
-        <v>718.29</v>
+        <v>844.73</v>
       </c>
       <c r="E15" s="27" t="n"/>
       <c r="F15" s="22">
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="D16" s="35" t="n">
-        <v>3080.75</v>
+        <v>3623.06</v>
       </c>
       <c r="E16" s="27" t="n"/>
       <c r="F16" s="22">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="D17" s="35" t="n">
-        <v>52700.12</v>
+        <v>73681.78</v>
       </c>
       <c r="E17" s="27" t="n"/>
       <c r="F17" s="22">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="D18" s="35" t="n">
-        <v>18564.26</v>
+        <v>25955.31</v>
       </c>
       <c r="E18" s="27" t="n"/>
       <c r="F18" s="22">
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="D19" s="35" t="n">
-        <v>1117.86</v>
+        <v>1562.91</v>
       </c>
       <c r="E19" s="27" t="n"/>
       <c r="F19" s="22">
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="D20" s="35" t="n">
-        <v>38409.98</v>
+        <v>45915.62</v>
       </c>
       <c r="E20" s="27" t="n"/>
       <c r="F20" s="22">
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="D21" s="35" t="n">
-        <v>7535.53</v>
+        <v>9008.040000000001</v>
       </c>
       <c r="E21" s="27" t="n"/>
       <c r="F21" s="22">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="D22" s="35" t="n">
-        <v>4334.02</v>
+        <v>5180.93</v>
       </c>
       <c r="E22" s="27" t="n"/>
       <c r="F22" s="22">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="D23" s="35" t="n">
-        <v>2169.07</v>
+        <v>2592.93</v>
       </c>
       <c r="E23" s="27" t="n"/>
       <c r="F23" s="22">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="D24" s="35" t="n">
-        <v>3953.48</v>
+        <v>4726.02</v>
       </c>
       <c r="E24" s="27" t="n"/>
       <c r="F24" s="22">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="D25" s="35" t="n">
-        <v>8312.6</v>
+        <v>9936.950000000001</v>
       </c>
       <c r="E25" s="27" t="n"/>
       <c r="F25" s="22">
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D26" s="35" t="n">
-        <v>201.46</v>
+        <v>240.82</v>
       </c>
       <c r="E26" s="27" t="n"/>
       <c r="F26" s="22">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="D27" s="35" t="n">
-        <v>708.55</v>
+        <v>847.01</v>
       </c>
       <c r="E27" s="27" t="n"/>
       <c r="F27" s="22">
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="D28" s="35" t="n">
-        <v>2887.44</v>
+        <v>3451.68</v>
       </c>
       <c r="E28" s="27" t="n"/>
       <c r="F28" s="22">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="D29" s="35" t="n">
-        <v>57308.2</v>
+        <v>81107.14</v>
       </c>
       <c r="E29" s="27" t="n"/>
       <c r="F29" s="22">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="D30" s="35" t="n">
-        <v>20355.53</v>
+        <v>28808.76</v>
       </c>
       <c r="E30" s="27" t="n"/>
       <c r="F30" s="22">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="D31" s="35" t="n">
-        <v>1755.2</v>
+        <v>2484.1</v>
       </c>
       <c r="E31" s="27" t="n"/>
       <c r="F31" s="22">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="D32" s="35" t="n">
-        <v>39151.59</v>
+        <v>43378.73</v>
       </c>
       <c r="E32" s="27" t="n"/>
       <c r="F32" s="22">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D33" s="35" t="n">
-        <v>8686.290000000001</v>
+        <v>9624.139999999999</v>
       </c>
       <c r="E33" s="27" t="n"/>
       <c r="F33" s="22">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="D34" s="35" t="n">
-        <v>4471.73</v>
+        <v>4954.54</v>
       </c>
       <c r="E34" s="27" t="n"/>
       <c r="F34" s="22">
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="D35" s="35" t="n">
-        <v>2110.12</v>
+        <v>2337.94</v>
       </c>
       <c r="E35" s="27" t="n"/>
       <c r="F35" s="22">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="D36" s="35" t="n">
-        <v>4659.53</v>
+        <v>5162.61</v>
       </c>
       <c r="E36" s="27" t="n"/>
       <c r="F36" s="22">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D37" s="35" t="n">
-        <v>8870.530000000001</v>
+        <v>9828.26</v>
       </c>
       <c r="E37" s="27" t="n"/>
       <c r="F37" s="22">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D38" s="35" t="n">
-        <v>4139.39</v>
+        <v>4586.31</v>
       </c>
       <c r="E38" s="27" t="n"/>
       <c r="F38" s="22">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="D39" s="35" t="n">
-        <v>206.06</v>
+        <v>228.31</v>
       </c>
       <c r="E39" s="27" t="n"/>
       <c r="F39" s="22">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="D40" s="35" t="n">
-        <v>696.8099999999999</v>
+        <v>772.05</v>
       </c>
       <c r="E40" s="27" t="n"/>
       <c r="F40" s="22">
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="D41" s="35" t="n">
-        <v>2912.63</v>
+        <v>3227.11</v>
       </c>
       <c r="E41" s="27" t="n"/>
       <c r="F41" s="22">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="D42" s="35" t="n">
-        <v>56295.88</v>
+        <v>78074.42</v>
       </c>
       <c r="E42" s="27" t="n"/>
       <c r="F42" s="22">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D43" s="35" t="n">
-        <v>21159.66</v>
+        <v>29345.46</v>
       </c>
       <c r="E43" s="27" t="n"/>
       <c r="F43" s="22">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D44" s="35" t="n">
-        <v>1716.19</v>
+        <v>2380.12</v>
       </c>
       <c r="E44" s="27" t="n"/>
       <c r="F44" s="22">
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="D45" s="35" t="n">
-        <v>38385.01</v>
+        <v>45807.37</v>
       </c>
       <c r="E45" s="27" t="n"/>
       <c r="F45" s="22">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="D46" s="35" t="n">
-        <v>8404.059999999999</v>
+        <v>10029.12</v>
       </c>
       <c r="E46" s="27" t="n"/>
       <c r="F46" s="22">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="D47" s="35" t="n">
-        <v>4328.51</v>
+        <v>5165.49</v>
       </c>
       <c r="E47" s="27" t="n"/>
       <c r="F47" s="22">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="D48" s="35" t="n">
-        <v>2108.57</v>
+        <v>2516.3</v>
       </c>
       <c r="E48" s="27" t="n"/>
       <c r="F48" s="22">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="D49" s="35" t="n">
-        <v>4495.73</v>
+        <v>5365.05</v>
       </c>
       <c r="E49" s="27" t="n"/>
       <c r="F49" s="22">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="D50" s="35" t="n">
-        <v>9169.99</v>
+        <v>10943.15</v>
       </c>
       <c r="E50" s="27" t="n"/>
       <c r="F50" s="22">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="D51" s="35" t="n">
-        <v>206.47</v>
+        <v>246.39</v>
       </c>
       <c r="E51" s="27" t="n"/>
       <c r="F51" s="22">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D52" s="35" t="n">
-        <v>2282.76</v>
+        <v>2724.16</v>
       </c>
       <c r="E52" s="27" t="n"/>
       <c r="F52" s="22">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D53" s="35" t="n">
-        <v>3102.95</v>
+        <v>3702.97</v>
       </c>
       <c r="E53" s="27" t="n"/>
       <c r="F53" s="22">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D54" s="35" t="n">
-        <v>59242.29</v>
+        <v>82553.08</v>
       </c>
       <c r="E54" s="27" t="n"/>
       <c r="F54" s="22">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="D55" s="35" t="n">
-        <v>23321.42</v>
+        <v>32497.99</v>
       </c>
       <c r="E55" s="27" t="n"/>
       <c r="F55" s="22">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="D56" s="35" t="n">
-        <v>2331.51</v>
+        <v>3248.93</v>
       </c>
       <c r="E56" s="27" t="n"/>
       <c r="F56" s="22">
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="D57" s="35" t="n">
-        <v>36975.82</v>
+        <v>42822.05</v>
       </c>
       <c r="E57" s="27" t="n"/>
       <c r="F57" s="22">
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="D58" s="35" t="n">
-        <v>10041.59</v>
+        <v>11629.25</v>
       </c>
       <c r="E58" s="27" t="n"/>
       <c r="F58" s="22">
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="D59" s="35" t="n">
-        <v>4486.8</v>
+        <v>5196.21</v>
       </c>
       <c r="E59" s="27" t="n"/>
       <c r="F59" s="22">
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="D60" s="35" t="n">
-        <v>2196.9</v>
+        <v>2544.25</v>
       </c>
       <c r="E60" s="27" t="n"/>
       <c r="F60" s="22">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="D61" s="35" t="n">
-        <v>5228.75</v>
+        <v>6055.46</v>
       </c>
       <c r="E61" s="27" t="n"/>
       <c r="F61" s="22">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="D62" s="35" t="n">
-        <v>9465.18</v>
+        <v>10961.72</v>
       </c>
       <c r="E62" s="27" t="n"/>
       <c r="F62" s="22">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="D63" s="35" t="n">
-        <v>205.31</v>
+        <v>237.77</v>
       </c>
       <c r="E63" s="27" t="n"/>
       <c r="F63" s="22">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="D64" s="35" t="n">
-        <v>724.24</v>
+        <v>838.74</v>
       </c>
       <c r="E64" s="27" t="n"/>
       <c r="F64" s="22">
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="D65" s="35" t="n">
-        <v>2948.39</v>
+        <v>3414.55</v>
       </c>
       <c r="E65" s="27" t="n"/>
       <c r="F65" s="22">
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="D66" s="35" t="n">
-        <v>57441.37</v>
+        <v>84457.42999999999</v>
       </c>
       <c r="E66" s="27" t="n"/>
       <c r="F66" s="22">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="D67" s="35" t="n">
-        <v>23075.4</v>
+        <v>33928.31</v>
       </c>
       <c r="E67" s="27" t="n"/>
       <c r="F67" s="22">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="D68" s="35" t="n">
-        <v>2390.12</v>
+        <v>3514.26</v>
       </c>
       <c r="E68" s="27" t="n"/>
       <c r="F68" s="22">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="D69" s="35" t="n">
-        <v>36749.1</v>
+        <v>45180.75</v>
       </c>
       <c r="E69" s="27" t="n"/>
       <c r="F69" s="22">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="D70" s="35" t="n">
-        <v>9994.700000000001</v>
+        <v>12287.87</v>
       </c>
       <c r="E70" s="27" t="n"/>
       <c r="F70" s="22">
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="D71" s="35" t="n">
-        <v>4295.01</v>
+        <v>5280.45</v>
       </c>
       <c r="E71" s="27" t="n"/>
       <c r="F71" s="22">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="D72" s="35" t="n">
-        <v>2068.55</v>
+        <v>2543.15</v>
       </c>
       <c r="E72" s="27" t="n"/>
       <c r="F72" s="22">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="D73" s="35" t="n">
-        <v>5114.26</v>
+        <v>6287.67</v>
       </c>
       <c r="E73" s="27" t="n"/>
       <c r="F73" s="22">
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="D74" s="35" t="n">
-        <v>9708.370000000001</v>
+        <v>11935.84</v>
       </c>
       <c r="E74" s="27" t="n"/>
       <c r="F74" s="22">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="D75" s="35" t="n">
-        <v>192.71</v>
+        <v>236.92</v>
       </c>
       <c r="E75" s="27" t="n"/>
       <c r="F75" s="22">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="D76" s="35" t="n">
-        <v>726.6</v>
+        <v>893.3099999999999</v>
       </c>
       <c r="E76" s="27" t="n"/>
       <c r="F76" s="22">
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="D77" s="35" t="n">
-        <v>2890.79</v>
+        <v>3554.04</v>
       </c>
       <c r="E77" s="27" t="n"/>
       <c r="F77" s="22">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="D78" s="35" t="n">
-        <v>62513.68</v>
+        <v>80700.86</v>
       </c>
       <c r="E78" s="27" t="n"/>
       <c r="F78" s="22">
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="D79" s="35" t="n">
-        <v>24148.94</v>
+        <v>31174.62</v>
       </c>
       <c r="E79" s="27" t="n"/>
       <c r="F79" s="22">
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="D80" s="35" t="n">
-        <v>2962.61</v>
+        <v>3824.52</v>
       </c>
       <c r="E80" s="27" t="n"/>
       <c r="F80" s="22">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="D81" s="35" t="n">
-        <v>42576.49</v>
+        <v>44467.27</v>
       </c>
       <c r="E81" s="27" t="n"/>
       <c r="F81" s="22">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="D82" s="35" t="n">
-        <v>9764.23</v>
+        <v>10197.85</v>
       </c>
       <c r="E82" s="27" t="n"/>
       <c r="F82" s="22">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="D83" s="35" t="n">
-        <v>4498.52</v>
+        <v>4698.3</v>
       </c>
       <c r="E83" s="27" t="n"/>
       <c r="F83" s="22">
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="D84" s="35" t="n">
-        <v>2095.6</v>
+        <v>2188.66</v>
       </c>
       <c r="E84" s="27" t="n"/>
       <c r="F84" s="22">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D85" s="35" t="n">
-        <v>5652.02</v>
+        <v>5903.02</v>
       </c>
       <c r="E85" s="27" t="n"/>
       <c r="F85" s="22">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="D86" s="35" t="n">
-        <v>9879.219999999999</v>
+        <v>10317.95</v>
       </c>
       <c r="E86" s="27" t="n"/>
       <c r="F86" s="22">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="D87" s="35" t="n">
-        <v>2887.53</v>
+        <v>3015.76</v>
       </c>
       <c r="E87" s="27" t="n"/>
       <c r="F87" s="22">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="D88" s="35" t="n">
-        <v>195.16</v>
+        <v>203.82</v>
       </c>
       <c r="E88" s="27" t="n"/>
       <c r="F88" s="22">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="D89" s="35" t="n">
-        <v>714.7</v>
+        <v>746.4400000000001</v>
       </c>
       <c r="E89" s="27" t="n"/>
       <c r="F89" s="22">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="D90" s="35" t="n">
-        <v>3026.51</v>
+        <v>3160.93</v>
       </c>
       <c r="E90" s="27" t="n"/>
       <c r="F90" s="22">
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="D91" s="35" t="n">
-        <v>59750.15</v>
+        <v>86273.66</v>
       </c>
       <c r="E91" s="27" t="n"/>
       <c r="F91" s="22">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="D92" s="35" t="n">
-        <v>23583.91</v>
+        <v>34052.97</v>
       </c>
       <c r="E92" s="27" t="n"/>
       <c r="F92" s="22">
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="D93" s="35" t="n">
-        <v>2959.59</v>
+        <v>4273.37</v>
       </c>
       <c r="E93" s="27" t="n"/>
       <c r="F93" s="22">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="D94" s="35" t="n">
-        <v>40389.36</v>
+        <v>45237.09</v>
       </c>
       <c r="E94" s="27" t="n"/>
       <c r="F94" s="22">
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="D95" s="35" t="n">
-        <v>11382.89</v>
+        <v>12749.11</v>
       </c>
       <c r="E95" s="27" t="n"/>
       <c r="F95" s="22">
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="D96" s="35" t="n">
-        <v>4463.28</v>
+        <v>4998.98</v>
       </c>
       <c r="E96" s="27" t="n"/>
       <c r="F96" s="22">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="D97" s="35" t="n">
-        <v>2107.19</v>
+        <v>2360.11</v>
       </c>
       <c r="E97" s="27" t="n"/>
       <c r="F97" s="22">
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="D98" s="35" t="n">
-        <v>5831.47</v>
+        <v>6531.39</v>
       </c>
       <c r="E98" s="27" t="n"/>
       <c r="F98" s="22">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="D99" s="35" t="n">
-        <v>9816.74</v>
+        <v>10994.99</v>
       </c>
       <c r="E99" s="27" t="n"/>
       <c r="F99" s="22">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="D100" s="35" t="n">
-        <v>201.53</v>
+        <v>225.72</v>
       </c>
       <c r="E100" s="27" t="n"/>
       <c r="F100" s="22">
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="D101" s="35" t="n">
-        <v>723.41</v>
+        <v>810.24</v>
       </c>
       <c r="E101" s="27" t="n"/>
       <c r="F101" s="22">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="D102" s="35" t="n">
-        <v>3028.83</v>
+        <v>3392.37</v>
       </c>
       <c r="E102" s="27" t="n"/>
       <c r="F102" s="22">
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="D103" s="35" t="n">
-        <v>65593.42</v>
+        <v>90057.73</v>
       </c>
       <c r="E103" s="27" t="n"/>
       <c r="F103" s="22">
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="D104" s="35" t="n">
-        <v>26534.91</v>
+        <v>36431.6</v>
       </c>
       <c r="E104" s="27" t="n"/>
       <c r="F104" s="22">
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="D105" s="35" t="n">
-        <v>3431.01</v>
+        <v>4710.67</v>
       </c>
       <c r="E105" s="27" t="n"/>
       <c r="F105" s="22">
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="D106" s="35" t="n">
-        <v>41722.62</v>
+        <v>46035.22</v>
       </c>
       <c r="E106" s="27" t="n"/>
       <c r="F106" s="22">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="D107" s="35" t="n">
-        <v>10749.54</v>
+        <v>11860.65</v>
       </c>
       <c r="E107" s="27" t="n"/>
       <c r="F107" s="22">
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="D108" s="35" t="n">
-        <v>4257.16</v>
+        <v>4697.2</v>
       </c>
       <c r="E108" s="27" t="n"/>
       <c r="F108" s="22">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="D109" s="35" t="n">
-        <v>2209.34</v>
+        <v>2437.71</v>
       </c>
       <c r="E109" s="27" t="n"/>
       <c r="F109" s="22">
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="D110" s="35" t="n">
-        <v>6510.99</v>
+        <v>7183.98</v>
       </c>
       <c r="E110" s="27" t="n"/>
       <c r="F110" s="22">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="D111" s="35" t="n">
-        <v>10137.12</v>
+        <v>11184.93</v>
       </c>
       <c r="E111" s="27" t="n"/>
       <c r="F111" s="22">
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="D112" s="35" t="n">
-        <v>198.64</v>
+        <v>219.18</v>
       </c>
       <c r="E112" s="27" t="n"/>
       <c r="F112" s="22">
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="D113" s="35" t="n">
-        <v>2717.27</v>
+        <v>2998.14</v>
       </c>
       <c r="E113" s="27" t="n"/>
       <c r="F113" s="22">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="D114" s="35" t="n">
-        <v>2884.81</v>
+        <v>3182.99</v>
       </c>
       <c r="E114" s="27" t="n"/>
       <c r="F114" s="22">
